--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middellaag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middellaag.xlsx
@@ -397,25 +397,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.58792005918047</v>
+        <v>0.5879200591804699</v>
       </c>
       <c r="C2">
-        <v>0.6481152217167628</v>
+        <v>0.6303542376453837</v>
       </c>
       <c r="D2">
         <v>1.313498814969672</v>
       </c>
       <c r="E2">
-        <v>0.6176863218124681</v>
+        <v>0.6162296117104964</v>
       </c>
       <c r="F2">
-        <v>0.5914781857011085</v>
+        <v>0.5914781857011084</v>
       </c>
       <c r="G2">
-        <v>0.7020990846397795</v>
+        <v>0.661573293841316</v>
       </c>
       <c r="H2">
-        <v>0.6186420519361094</v>
+        <v>0.6170674173655764</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -426,22 +426,22 @@
         <v>0.6195689296840667</v>
       </c>
       <c r="C3">
-        <v>0.6614835697473717</v>
+        <v>0.6453361537028188</v>
       </c>
       <c r="D3">
         <v>1.225690816709213</v>
       </c>
       <c r="E3">
-        <v>0.6298513683933809</v>
+        <v>0.628504755825571</v>
       </c>
       <c r="F3">
         <v>0.620716112768283</v>
       </c>
       <c r="G3">
-        <v>0.7079339602863506</v>
+        <v>0.6738667883227225</v>
       </c>
       <c r="H3">
-        <v>0.6301294040625675</v>
+        <v>0.6287509832441502</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -452,22 +452,22 @@
         <v>0.5318206555514727</v>
       </c>
       <c r="C4">
-        <v>0.686674897387055</v>
+        <v>0.6212544359327956</v>
       </c>
       <c r="D4">
         <v>0.7754902945783939</v>
       </c>
       <c r="E4">
-        <v>0.6008184859805357</v>
+        <v>0.5997027265756183</v>
       </c>
       <c r="F4">
         <v>0.5365522613848597</v>
       </c>
       <c r="G4">
-        <v>0.6671393909086752</v>
+        <v>0.6187979655781662</v>
       </c>
       <c r="H4">
-        <v>0.6016267990582209</v>
+        <v>0.6003834763058934</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -475,25 +475,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.6651261304297056</v>
+        <v>0.6651261304297055</v>
       </c>
       <c r="C5">
-        <v>0.7474217523297062</v>
+        <v>0.7087126653779002</v>
       </c>
       <c r="D5">
         <v>0.449441296965801</v>
       </c>
       <c r="E5">
-        <v>0.6507913071018955</v>
+        <v>0.6478799216700447</v>
       </c>
       <c r="F5">
-        <v>0.6639177403196133</v>
+        <v>0.6639177403196131</v>
       </c>
       <c r="G5">
-        <v>0.7116557279080611</v>
+        <v>0.6897892064502114</v>
       </c>
       <c r="H5">
-        <v>0.6504375157112866</v>
+        <v>0.6475765481738003</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -501,25 +501,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.6534093172196863</v>
+        <v>0.6534093172196862</v>
       </c>
       <c r="C6">
-        <v>0.741508040369947</v>
+        <v>0.6926616539226804</v>
       </c>
       <c r="D6">
         <v>0.3270940533934479</v>
       </c>
       <c r="E6">
-        <v>0.6465461535710778</v>
+        <v>0.6436767073653823</v>
       </c>
       <c r="F6">
-        <v>0.6526352638223126</v>
+        <v>0.6526352638223125</v>
       </c>
       <c r="G6">
-        <v>0.6921269154972672</v>
+        <v>0.6652366117247697</v>
       </c>
       <c r="H6">
-        <v>0.6462407761099619</v>
+        <v>0.6434202094109371</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -527,25 +527,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.6810079994693606</v>
+        <v>0.6810079994693605</v>
       </c>
       <c r="C7">
-        <v>0.7772848066723598</v>
+        <v>0.7150384956991823</v>
       </c>
       <c r="D7">
         <v>0.4013754906414626</v>
       </c>
       <c r="E7">
-        <v>0.6549461698890082</v>
+        <v>0.651985040046865</v>
       </c>
       <c r="F7">
-        <v>0.6794437767110588</v>
+        <v>0.6794437767110587</v>
       </c>
       <c r="G7">
-        <v>0.7311301017741306</v>
+        <v>0.6933145588868495</v>
       </c>
       <c r="H7">
-        <v>0.6545881918591552</v>
+        <v>0.6516786648199745</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -553,25 +553,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.6067621287882927</v>
+        <v>0.6067621287882924</v>
       </c>
       <c r="C8">
-        <v>0.4770173116373552</v>
+        <v>0.5363111047676458</v>
       </c>
       <c r="D8">
         <v>0.2902973021720563</v>
       </c>
       <c r="E8">
-        <v>0.5961646260276713</v>
+        <v>0.5996683719996172</v>
       </c>
       <c r="F8">
         <v>0.6051242423863379</v>
       </c>
       <c r="G8">
-        <v>0.4825273335458954</v>
+        <v>0.5333783912550941</v>
       </c>
       <c r="H8">
-        <v>0.5957902921233157</v>
+        <v>0.5993296787741017</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -582,22 +582,22 @@
         <v>0.687597352504432</v>
       </c>
       <c r="C9">
-        <v>0.7037044247573736</v>
+        <v>0.6933101177503062</v>
       </c>
       <c r="D9">
         <v>0.688065013977329</v>
       </c>
       <c r="E9">
-        <v>0.6497804739386871</v>
+        <v>0.6473501211790124</v>
       </c>
       <c r="F9">
         <v>0.6862152739235847</v>
       </c>
       <c r="G9">
-        <v>0.6760054899001348</v>
+        <v>0.6843487676573281</v>
       </c>
       <c r="H9">
-        <v>0.6495261151428007</v>
+        <v>0.6471348910781336</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -605,25 +605,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.6962885743215873</v>
+        <v>0.6962885743215872</v>
       </c>
       <c r="C10">
-        <v>0.7646709075939094</v>
+        <v>0.7155094639707574</v>
       </c>
       <c r="D10">
         <v>0.793999102161678</v>
       </c>
       <c r="E10">
-        <v>0.6557084768085584</v>
+        <v>0.6527625053743096</v>
       </c>
       <c r="F10">
         <v>0.6951162783554444</v>
       </c>
       <c r="G10">
-        <v>0.7598594951260311</v>
+        <v>0.7168369832582071</v>
       </c>
       <c r="H10">
-        <v>0.6558522342525583</v>
+        <v>0.6529559516647887</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -631,25 +631,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.6892710809081366</v>
+        <v>0.6892710809081365</v>
       </c>
       <c r="C11">
-        <v>0.7666761451581852</v>
+        <v>0.7140132558073445</v>
       </c>
       <c r="D11">
         <v>0.6895836588783807</v>
       </c>
       <c r="E11">
-        <v>0.6560590397357804</v>
+        <v>0.6532446931006516</v>
       </c>
       <c r="F11">
         <v>0.6880779658990894</v>
       </c>
       <c r="G11">
-        <v>0.7556771256224231</v>
+        <v>0.7094089328744574</v>
       </c>
       <c r="H11">
-        <v>0.6560788917135243</v>
+        <v>0.653316056718384</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -657,25 +657,25 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.6241881254001516</v>
+        <v>0.6241881254001515</v>
       </c>
       <c r="C12">
-        <v>0.7745554222486973</v>
+        <v>0.7313851181014966</v>
       </c>
       <c r="D12">
         <v>0.1984769673372521</v>
       </c>
       <c r="E12">
-        <v>0.6464965173239271</v>
+        <v>0.6435563152521299</v>
       </c>
       <c r="F12">
         <v>0.6241101731037968</v>
       </c>
       <c r="G12">
-        <v>0.7231763437576213</v>
+        <v>0.7037786893688498</v>
       </c>
       <c r="H12">
-        <v>0.6462765158710355</v>
+        <v>0.6433822284364239</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -686,22 +686,22 @@
         <v>0.6925478065089196</v>
       </c>
       <c r="C13">
-        <v>0.76333231959312</v>
+        <v>0.7108772263761759</v>
       </c>
       <c r="D13">
         <v>0.6163823604628738</v>
       </c>
       <c r="E13">
-        <v>0.6546031863939528</v>
+        <v>0.6516205864456877</v>
       </c>
       <c r="F13">
         <v>0.6912035447731096</v>
       </c>
       <c r="G13">
-        <v>0.7490676502734643</v>
+        <v>0.7043203983323243</v>
       </c>
       <c r="H13">
-        <v>0.6546671971422592</v>
+        <v>0.6517377128140355</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middellaag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middellaag.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middellaag.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_middellaag.xlsx
@@ -403,25 +403,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.5879200591804699</v>
+        <v>0.9348736580360384</v>
       </c>
       <c r="C2">
-        <v>0.6303542376453837</v>
+        <v>1.002349831076548</v>
       </c>
       <c r="D2">
-        <v>1.313498814969672</v>
+        <v>2.088643554173683</v>
       </c>
       <c r="E2">
-        <v>0.6162296117104964</v>
+        <v>0.9798897355075256</v>
       </c>
       <c r="F2">
-        <v>0.5914781857011084</v>
+        <v>0.9405315679919283</v>
       </c>
       <c r="G2">
-        <v>0.661573293841316</v>
+        <v>1.051992419062077</v>
       </c>
       <c r="H2">
-        <v>0.6170674173655764</v>
+        <v>0.9812219615904045</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -429,25 +429,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.6195689296840667</v>
+        <v>0.6361473297347028</v>
       </c>
       <c r="C3">
-        <v>0.6453361537028188</v>
+        <v>0.6626040320786434</v>
       </c>
       <c r="D3">
-        <v>1.225690816709213</v>
+        <v>1.258487801393642</v>
       </c>
       <c r="E3">
-        <v>0.628504755825571</v>
+        <v>0.6453222603462011</v>
       </c>
       <c r="F3">
-        <v>0.620716112768283</v>
+        <v>0.6373252090969121</v>
       </c>
       <c r="G3">
-        <v>0.6738667883227225</v>
+        <v>0.6918980882514457</v>
       </c>
       <c r="H3">
-        <v>0.6287509832441502</v>
+        <v>0.6455750763079641</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -455,25 +455,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.5318206555514727</v>
+        <v>0.6896874185678047</v>
       </c>
       <c r="C4">
-        <v>0.6212544359327956</v>
+        <v>0.8056689105991625</v>
       </c>
       <c r="D4">
-        <v>0.7754902945783939</v>
+        <v>1.005688466232191</v>
       </c>
       <c r="E4">
-        <v>0.5997027265756183</v>
+        <v>0.7777197464643806</v>
       </c>
       <c r="F4">
-        <v>0.5365522613848597</v>
+        <v>0.6958235642380495</v>
       </c>
       <c r="G4">
-        <v>0.6187979655781662</v>
+        <v>0.8024832564129485</v>
       </c>
       <c r="H4">
-        <v>0.6003834763058934</v>
+        <v>0.7786025713777481</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -481,25 +481,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.6651261304297055</v>
+        <v>0.1667963361139509</v>
       </c>
       <c r="C5">
-        <v>0.7087126653779002</v>
+        <v>0.1777267055591638</v>
       </c>
       <c r="D5">
-        <v>0.449441296965801</v>
+        <v>0.1127081890223835</v>
       </c>
       <c r="E5">
-        <v>0.6478799216700447</v>
+        <v>0.1624714354652433</v>
       </c>
       <c r="F5">
-        <v>0.6639177403196131</v>
+        <v>0.1664933032999649</v>
       </c>
       <c r="G5">
-        <v>0.6897892064502114</v>
+        <v>0.1729811941872047</v>
       </c>
       <c r="H5">
-        <v>0.6475765481738003</v>
+        <v>0.1623953572819747</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -507,25 +507,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.6534093172196862</v>
+        <v>0.5660279443159711</v>
       </c>
       <c r="C6">
-        <v>0.6926616539226804</v>
+        <v>0.6000310092678657</v>
       </c>
       <c r="D6">
-        <v>0.3270940533934479</v>
+        <v>0.2833512926140652</v>
       </c>
       <c r="E6">
-        <v>0.6436767073653823</v>
+        <v>0.5575968904520595</v>
       </c>
       <c r="F6">
-        <v>0.6526352638223125</v>
+        <v>0.5653574061988069</v>
       </c>
       <c r="G6">
-        <v>0.6652366117247697</v>
+        <v>0.5762735576231368</v>
       </c>
       <c r="H6">
-        <v>0.6434202094109371</v>
+        <v>0.5573746943399905</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -533,25 +533,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.6810079994693605</v>
+        <v>0.6469575994958926</v>
       </c>
       <c r="C7">
-        <v>0.7150384956991823</v>
+        <v>0.6792865709142233</v>
       </c>
       <c r="D7">
-        <v>0.4013754906414626</v>
+        <v>0.3813067161093896</v>
       </c>
       <c r="E7">
-        <v>0.651985040046865</v>
+        <v>0.6193857880445217</v>
       </c>
       <c r="F7">
-        <v>0.6794437767110587</v>
+        <v>0.6454715878755057</v>
       </c>
       <c r="G7">
-        <v>0.6933145588868495</v>
+        <v>0.658648830942507</v>
       </c>
       <c r="H7">
-        <v>0.6516786648199745</v>
+        <v>0.6190947315789758</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -559,25 +559,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.6067621287882924</v>
+        <v>0.1518287258188743</v>
       </c>
       <c r="C8">
-        <v>0.5363111047676458</v>
+        <v>0.134199924181154</v>
       </c>
       <c r="D8">
-        <v>0.2902973021720563</v>
+        <v>0.0726404424505844</v>
       </c>
       <c r="E8">
-        <v>0.5996683719996172</v>
+        <v>0.1500536709771286</v>
       </c>
       <c r="F8">
-        <v>0.6051242423863379</v>
+        <v>0.151418881180183</v>
       </c>
       <c r="G8">
-        <v>0.5333783912550941</v>
+        <v>0.1334660778603697</v>
       </c>
       <c r="H8">
-        <v>0.5993296787741017</v>
+        <v>0.1499689205313877</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -585,25 +585,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.687597352504432</v>
+        <v>0.8005554229795351</v>
       </c>
       <c r="C9">
-        <v>0.6933101177503062</v>
+        <v>0.807206677788961</v>
       </c>
       <c r="D9">
-        <v>0.688065013977329</v>
+        <v>0.8010999115917771</v>
       </c>
       <c r="E9">
-        <v>0.6473501211790124</v>
+        <v>0.7536964012277483</v>
       </c>
       <c r="F9">
-        <v>0.6862152739235847</v>
+        <v>0.7989462973788461</v>
       </c>
       <c r="G9">
-        <v>0.6843487676573281</v>
+        <v>0.7967731626103152</v>
       </c>
       <c r="H9">
-        <v>0.6471348910781336</v>
+        <v>0.7534458132581765</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -611,25 +611,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.6962885743215872</v>
+        <v>0.1730659462186604</v>
       </c>
       <c r="C10">
-        <v>0.7155094639707574</v>
+        <v>0.1778433927788587</v>
       </c>
       <c r="D10">
-        <v>0.793999102161678</v>
+        <v>0.1973523779939431</v>
       </c>
       <c r="E10">
-        <v>0.6527625053743096</v>
+        <v>0.1622473279254065</v>
       </c>
       <c r="F10">
-        <v>0.6951162783554444</v>
+        <v>0.17277456629644</v>
       </c>
       <c r="G10">
-        <v>0.7168369832582071</v>
+        <v>0.178173354220248</v>
       </c>
       <c r="H10">
-        <v>0.6529559516647887</v>
+        <v>0.1622954099513637</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -637,25 +637,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.6892710809081365</v>
+        <v>0.166759132477775</v>
       </c>
       <c r="C11">
-        <v>0.7140132558073445</v>
+        <v>0.172745142534035</v>
       </c>
       <c r="D11">
-        <v>0.6895836588783807</v>
+        <v>0.1668347561802534</v>
       </c>
       <c r="E11">
-        <v>0.6532446931006516</v>
+        <v>0.158043070911448</v>
       </c>
       <c r="F11">
-        <v>0.6880779658990894</v>
+        <v>0.1664704756207474</v>
       </c>
       <c r="G11">
-        <v>0.7094089328744574</v>
+        <v>0.1716311934373687</v>
       </c>
       <c r="H11">
-        <v>0.653316056718384</v>
+        <v>0.1580603363028349</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -663,25 +663,25 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.6241881254001515</v>
+        <v>0.5341390823245975</v>
       </c>
       <c r="C12">
-        <v>0.7313851181014966</v>
+        <v>0.6258712075917138</v>
       </c>
       <c r="D12">
-        <v>0.1984769673372521</v>
+        <v>0.1698435149308966</v>
       </c>
       <c r="E12">
-        <v>0.6435563152521299</v>
+        <v>0.5507131034134995</v>
       </c>
       <c r="F12">
-        <v>0.6241101731037968</v>
+        <v>0.5340723758841101</v>
       </c>
       <c r="G12">
-        <v>0.7037786893688498</v>
+        <v>0.6022474443231282</v>
       </c>
       <c r="H12">
-        <v>0.6433822284364239</v>
+        <v>0.5505641313837506</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -689,25 +689,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.6925478065089196</v>
+        <v>0.1704733062175802</v>
       </c>
       <c r="C13">
-        <v>0.7108772263761759</v>
+        <v>0.174985163415674</v>
       </c>
       <c r="D13">
-        <v>0.6163823604628738</v>
+        <v>0.1517248887293227</v>
       </c>
       <c r="E13">
-        <v>0.6516205864456877</v>
+        <v>0.1603989135866308</v>
       </c>
       <c r="F13">
-        <v>0.6912035447731096</v>
+        <v>0.1701424110210731</v>
       </c>
       <c r="G13">
-        <v>0.7043203983323243</v>
+        <v>0.1733711749741106</v>
       </c>
       <c r="H13">
-        <v>0.6517377128140355</v>
+        <v>0.1604277446926857</v>
       </c>
     </row>
   </sheetData>
